--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260703.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260703.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>254,742,233</t>
+          <t>2,240,216</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,240,216</t>
+          <t>254,742,233</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>327,650,011</t>
+          <t>276,805,134</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>276,805,134</t>
+          <t>327,650,011</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>16,436,054</t>
+          <t>24,587,814</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>24,587,814</t>
+          <t>16,436,054</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>23,434,976</t>
+          <t>1,700,274</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1,700,274</t>
+          <t>23,434,976</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
